--- a/AAII_Financials/Quarterly/MSGM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MSGM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="92">
   <si>
     <t>MSGM</t>
   </si>
@@ -656,127 +656,128 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
@@ -789,40 +790,43 @@
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E8" s="3">
         <v>4000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3000</v>
-      </c>
-      <c r="M8" s="3">
-        <v>1700</v>
       </c>
       <c r="N8" s="3">
         <v>1700</v>
@@ -834,44 +838,44 @@
         <v>1700</v>
       </c>
       <c r="Q8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="R8" s="3">
         <v>3800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>16100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3200</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
@@ -884,89 +888,92 @@
       <c r="AG8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>600</v>
+      </c>
+      <c r="E9" s="3">
         <v>500</v>
-      </c>
-      <c r="E9" s="3">
-        <v>600</v>
       </c>
       <c r="F9" s="3">
         <v>600</v>
       </c>
       <c r="G9" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H9" s="3">
         <v>500</v>
       </c>
       <c r="I9" s="3">
+        <v>500</v>
+      </c>
+      <c r="J9" s="3">
         <v>1100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>800</v>
-      </c>
-      <c r="L9" s="3">
-        <v>700</v>
       </c>
       <c r="M9" s="3">
         <v>700</v>
       </c>
       <c r="N9" s="3">
+        <v>700</v>
+      </c>
+      <c r="O9" s="3">
         <v>800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4900</v>
-      </c>
-      <c r="V9" s="3">
-        <v>900</v>
       </c>
       <c r="W9" s="3">
         <v>900</v>
       </c>
       <c r="X9" s="3">
+        <v>900</v>
+      </c>
+      <c r="Y9" s="3">
         <v>800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1100</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
@@ -979,89 +986,92 @@
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E10" s="3">
         <v>3500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>900</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1100</v>
       </c>
       <c r="K10" s="3">
         <v>1100</v>
       </c>
       <c r="L10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M10" s="3">
         <v>2400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1100</v>
-      </c>
-      <c r="N10" s="3">
-        <v>900</v>
       </c>
       <c r="O10" s="3">
         <v>900</v>
       </c>
       <c r="P10" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q10" s="3">
         <v>500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>10800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2100</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1074,8 +1084,11 @@
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1109,89 +1122,90 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E12" s="3">
         <v>500</v>
       </c>
       <c r="F12" s="3">
+        <v>500</v>
+      </c>
+      <c r="G12" s="3">
         <v>400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>300</v>
-      </c>
-      <c r="H12" s="3">
-        <v>600</v>
       </c>
       <c r="I12" s="3">
         <v>600</v>
       </c>
       <c r="J12" s="3">
+        <v>600</v>
+      </c>
+      <c r="K12" s="3">
         <v>800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>900</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1204,8 +1218,11 @@
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1299,68 +1316,71 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>1300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>-800</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J14" s="3">
         <v>-600</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>-300</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>-3000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>4000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>200</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>9300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1376,8 +1396,8 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1394,8 +1414,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1421,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3">
         <v>100</v>
@@ -1460,22 +1483,22 @@
         <v>100</v>
       </c>
       <c r="X15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
       </c>
       <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
         <v>100</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
-      </c>
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>3</v>
+      <c r="AC15" s="3">
+        <v>0</v>
       </c>
       <c r="AD15" s="3" t="s">
         <v>3</v>
@@ -1489,8 +1512,11 @@
       <c r="AG15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1521,8 +1547,9 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1530,80 +1557,80 @@
         <v>2900</v>
       </c>
       <c r="E17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F17" s="3">
         <v>2000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4200</v>
-      </c>
-      <c r="M17" s="3">
-        <v>4400</v>
       </c>
       <c r="N17" s="3">
         <v>4400</v>
       </c>
       <c r="O17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="P17" s="3">
         <v>6300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>17900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>13300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3400</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1616,89 +1643,92 @@
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>600</v>
+      </c>
+      <c r="E18" s="3">
         <v>1100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1200</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-2700</v>
       </c>
       <c r="N18" s="3">
         <v>-2700</v>
       </c>
       <c r="O18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="P18" s="3">
         <v>-4600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-6700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-15600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-6800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-6400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-6000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-15400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-200</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1711,8 +1741,11 @@
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1746,88 +1779,89 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-2300</v>
       </c>
-      <c r="H20" s="3">
-        <v>-1100</v>
-      </c>
       <c r="I20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J20" s="3">
         <v>2200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
+      <c r="AC20" s="3">
+        <v>0</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
@@ -1841,89 +1875,92 @@
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>300</v>
+      </c>
+      <c r="E21" s="3">
         <v>1000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3500</v>
       </c>
-      <c r="H21" s="3">
-        <v>1100</v>
-      </c>
       <c r="I21" s="3">
+        <v>900</v>
+      </c>
+      <c r="J21" s="3">
         <v>-3400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-6800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-15200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-6200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-5900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-5400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-13800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-100</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1936,8 +1973,11 @@
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1969,10 +2009,10 @@
         <v>0</v>
       </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
-      </c>
-      <c r="N22" s="3">
-        <v>200</v>
       </c>
       <c r="O22" s="3">
         <v>200</v>
@@ -1981,10 +2021,10 @@
         <v>200</v>
       </c>
       <c r="Q22" s="3">
+        <v>200</v>
+      </c>
+      <c r="R22" s="3">
         <v>500</v>
-      </c>
-      <c r="R22" s="3">
-        <v>200</v>
       </c>
       <c r="S22" s="3">
         <v>200</v>
@@ -1999,23 +2039,23 @@
         <v>200</v>
       </c>
       <c r="W22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
         <v>100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>200</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
@@ -2031,89 +2071,92 @@
       <c r="AG22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>200</v>
+      </c>
+      <c r="E23" s="3">
         <v>1000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-8200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-7500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-16000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-7000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-14100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2400</v>
       </c>
-      <c r="AA23" s="3">
-        <v>0</v>
-      </c>
       <c r="AB23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="3">
         <v>-200</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2126,20 +2169,23 @@
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2170,8 +2216,8 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2221,8 +2267,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2316,89 +2365,92 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>200</v>
+      </c>
+      <c r="E26" s="3">
         <v>1000</v>
-      </c>
-      <c r="E26" s="3">
-        <v>800</v>
       </c>
       <c r="F26" s="3">
         <v>800</v>
       </c>
       <c r="G26" s="3">
+        <v>800</v>
+      </c>
+      <c r="H26" s="3">
         <v>4200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-8200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-16000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-14100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2400</v>
       </c>
-      <c r="AA26" s="3">
-        <v>0</v>
-      </c>
       <c r="AB26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-200</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2411,89 +2463,92 @@
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>400</v>
+      </c>
+      <c r="E27" s="3">
         <v>300</v>
-      </c>
-      <c r="E27" s="3">
-        <v>800</v>
       </c>
       <c r="F27" s="3">
         <v>800</v>
       </c>
       <c r="G27" s="3">
+        <v>800</v>
+      </c>
+      <c r="H27" s="3">
         <v>4300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-15100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-13800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-200</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2506,8 +2561,11 @@
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2601,8 +2659,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2696,8 +2757,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2791,8 +2855,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2886,88 +2953,91 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>2300</v>
       </c>
-      <c r="H32" s="3">
-        <v>1100</v>
-      </c>
       <c r="I32" s="3">
+        <v>900</v>
+      </c>
+      <c r="J32" s="3">
         <v>-2200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
+      <c r="AC32" s="3">
+        <v>0</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
@@ -2981,89 +3051,92 @@
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>400</v>
+      </c>
+      <c r="E33" s="3">
         <v>300</v>
-      </c>
-      <c r="E33" s="3">
-        <v>800</v>
       </c>
       <c r="F33" s="3">
         <v>800</v>
       </c>
       <c r="G33" s="3">
+        <v>800</v>
+      </c>
+      <c r="H33" s="3">
         <v>4300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-15100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-13800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-200</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
@@ -3076,8 +3149,11 @@
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3171,89 +3247,92 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>400</v>
+      </c>
+      <c r="E35" s="3">
         <v>300</v>
-      </c>
-      <c r="E35" s="3">
-        <v>800</v>
       </c>
       <c r="F35" s="3">
         <v>800</v>
       </c>
       <c r="G35" s="3">
+        <v>800</v>
+      </c>
+      <c r="H35" s="3">
         <v>4300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-15100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-13800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-200</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3266,94 +3345,97 @@
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3366,8 +3448,11 @@
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3401,8 +3486,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3436,83 +3522,84 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E41" s="3">
         <v>5900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>12400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>17800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>22200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>28300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>49800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3100</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3531,8 +3618,11 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3626,83 +3716,86 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E43" s="3">
         <v>2300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1400</v>
-      </c>
-      <c r="M43" s="3">
-        <v>700</v>
       </c>
       <c r="N43" s="3">
         <v>700</v>
       </c>
       <c r="O43" s="3">
+        <v>700</v>
+      </c>
+      <c r="P43" s="3">
         <v>1100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8400</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3721,8 +3814,11 @@
       <c r="AG43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3765,8 +3861,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3816,8 +3912,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3827,12 +3926,12 @@
       <c r="E45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3860,39 +3959,39 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>1000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2300</v>
-      </c>
-      <c r="S45" s="3">
-        <v>1700</v>
       </c>
       <c r="T45" s="3">
         <v>1700</v>
       </c>
       <c r="U45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V45" s="3">
         <v>1200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>600</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3911,83 +4010,86 @@
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E46" s="3">
         <v>9100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>16900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>24600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>27900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>33500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>56200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>10500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12000</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4006,8 +4108,11 @@
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4050,8 +4155,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4101,8 +4206,11 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4125,59 +4233,59 @@
         <v>100</v>
       </c>
       <c r="J48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K48" s="3">
         <v>200</v>
       </c>
       <c r="L48" s="3">
+        <v>200</v>
+      </c>
+      <c r="M48" s="3">
         <v>300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1400</v>
-      </c>
-      <c r="U48" s="3">
-        <v>700</v>
       </c>
       <c r="V48" s="3">
         <v>700</v>
       </c>
       <c r="W48" s="3">
+        <v>700</v>
+      </c>
+      <c r="X48" s="3">
         <v>500</v>
-      </c>
-      <c r="X48" s="3">
-        <v>200</v>
       </c>
       <c r="Y48" s="3">
         <v>200</v>
       </c>
       <c r="Z48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA48" s="3">
         <v>100</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4196,83 +4304,86 @@
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E49" s="3">
         <v>4100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3700</v>
-      </c>
-      <c r="G49" s="3">
-        <v>3300</v>
       </c>
       <c r="H49" s="3">
         <v>3300</v>
       </c>
       <c r="I49" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J49" s="3">
         <v>3400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13000</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>13400</v>
       </c>
       <c r="R49" s="3">
         <v>13400</v>
       </c>
       <c r="S49" s="3">
+        <v>13400</v>
+      </c>
+      <c r="T49" s="3">
         <v>14300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>15300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>25400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>26500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>24800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5900</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4291,8 +4402,11 @@
       <c r="AG49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4386,8 +4500,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4481,8 +4598,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4492,8 +4612,8 @@
       <c r="E52" s="3">
         <v>100</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
+      <c r="F52" s="3">
+        <v>100</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
@@ -4525,8 +4645,8 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -4550,14 +4670,14 @@
         <v>0</v>
       </c>
       <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
         <v>1000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>500</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4576,8 +4696,11 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4671,83 +4794,86 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E54" s="3">
         <v>13900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7200</v>
-      </c>
-      <c r="L54" s="3">
-        <v>9800</v>
       </c>
       <c r="M54" s="3">
         <v>9800</v>
       </c>
       <c r="N54" s="3">
+        <v>9800</v>
+      </c>
+      <c r="O54" s="3">
         <v>11400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>13300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>22100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>18900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>20800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>25000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>33600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>50700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>55000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>58700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>66000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>17400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>18600</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4766,8 +4892,11 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4801,8 +4930,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4836,83 +4966,84 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>900</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1000</v>
       </c>
       <c r="G57" s="3">
         <v>1000</v>
       </c>
       <c r="H57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I57" s="3">
         <v>2700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>600</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4931,16 +5062,19 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -4958,13 +5092,13 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L58" s="3">
         <v>100</v>
       </c>
       <c r="M58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N58" s="3">
         <v>200</v>
@@ -4973,41 +5107,41 @@
         <v>200</v>
       </c>
       <c r="P58" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q58" s="3">
         <v>300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>300</v>
-      </c>
-      <c r="U58" s="3">
-        <v>100</v>
       </c>
       <c r="V58" s="3">
         <v>100</v>
       </c>
       <c r="W58" s="3">
+        <v>100</v>
+      </c>
+      <c r="X58" s="3">
         <v>300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>10900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>10400</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5017,8 +5151,8 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE58" s="3">
-        <v>0</v>
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF58" s="3">
         <v>0</v>
@@ -5026,83 +5160,86 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F59" s="3">
         <v>1300</v>
       </c>
-      <c r="E59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1200</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1400</v>
       </c>
       <c r="J59" s="3">
         <v>1400</v>
       </c>
       <c r="K59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L59" s="3">
         <v>1600</v>
-      </c>
-      <c r="L59" s="3">
-        <v>5600</v>
       </c>
       <c r="M59" s="3">
         <v>5600</v>
       </c>
       <c r="N59" s="3">
+        <v>5600</v>
+      </c>
+      <c r="O59" s="3">
         <v>3900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2000</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5121,83 +5258,86 @@
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E60" s="3">
         <v>3900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>14900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>13000</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5216,13 +5356,16 @@
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -5252,29 +5395,29 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>100</v>
       </c>
       <c r="P61" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q61" s="3">
         <v>300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>500</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -5311,8 +5454,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5320,11 +5466,11 @@
         <v>1200</v>
       </c>
       <c r="E62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F62" s="3">
         <v>800</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
       <c r="G62" s="3">
         <v>0</v>
       </c>
@@ -5347,34 +5493,34 @@
         <v>0</v>
       </c>
       <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
         <v>2900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3500</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>3100</v>
       </c>
       <c r="R62" s="3">
         <v>3100</v>
       </c>
       <c r="S62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="T62" s="3">
         <v>3500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3800</v>
-      </c>
-      <c r="W62" s="3">
-        <v>900</v>
       </c>
       <c r="X62" s="3">
         <v>900</v>
@@ -5385,8 +5531,8 @@
       <c r="Z62" s="3">
         <v>900</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
+      <c r="AA62" s="3">
+        <v>900</v>
       </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
@@ -5406,8 +5552,11 @@
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5501,8 +5650,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5596,8 +5748,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5691,83 +5846,86 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E66" s="3">
         <v>5300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>17400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>18400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>19900</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5786,8 +5944,11 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5821,8 +5982,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5916,8 +6078,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6011,8 +6176,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6106,8 +6274,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6201,77 +6372,80 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-84600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-84500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-84900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-85700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-86500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-90700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-91800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-86300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-86400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-88700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-89000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-90700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-87300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-79100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-74000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-69000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-60500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-53100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-38000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-31000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-24400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-18600</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6296,8 +6470,11 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6391,8 +6568,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6486,8 +6666,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6581,83 +6764,86 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E76" s="3">
         <v>7100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>21800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>36700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>43800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>50600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>57300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6676,8 +6862,11 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6771,94 +6960,97 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6871,89 +7063,92 @@
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>400</v>
+      </c>
+      <c r="E81" s="3">
         <v>300</v>
-      </c>
-      <c r="E81" s="3">
-        <v>800</v>
       </c>
       <c r="F81" s="3">
         <v>800</v>
       </c>
       <c r="G81" s="3">
+        <v>800</v>
+      </c>
+      <c r="H81" s="3">
         <v>4300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-15100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-13800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-200</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6966,8 +7161,11 @@
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7001,31 +7199,32 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E83" s="3">
+        <v>100</v>
+      </c>
+      <c r="F83" s="3">
         <v>-600</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
       <c r="G83" s="3">
         <v>0</v>
       </c>
       <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-800</v>
-      </c>
-      <c r="J83" s="3">
-        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
@@ -7034,19 +7233,19 @@
         <v>100</v>
       </c>
       <c r="M83" s="3">
+        <v>100</v>
+      </c>
+      <c r="N83" s="3">
         <v>-900</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
         <v>200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>100</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>500</v>
       </c>
       <c r="R83" s="3">
         <v>500</v>
@@ -7055,7 +7254,7 @@
         <v>500</v>
       </c>
       <c r="T83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="U83" s="3">
         <v>600</v>
@@ -7064,26 +7263,26 @@
         <v>600</v>
       </c>
       <c r="W83" s="3">
+        <v>600</v>
+      </c>
+      <c r="X83" s="3">
         <v>500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>100</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7096,8 +7295,11 @@
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7191,8 +7393,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7286,8 +7491,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7381,8 +7589,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7476,8 +7687,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7571,89 +7785,92 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E89" s="3">
         <v>1600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2100</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
       <c r="H89" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I89" s="3">
+        <v>400</v>
+      </c>
+      <c r="J89" s="3">
         <v>-1100</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-700</v>
       </c>
       <c r="K89" s="3">
         <v>-700</v>
       </c>
       <c r="L89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M89" s="3">
         <v>-400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-6500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-5500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>600</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7666,8 +7883,11 @@
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7701,8 +7921,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7715,14 +7936,14 @@
       <c r="F91" s="3">
         <v>0</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
+      <c r="G91" s="3">
+        <v>0</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -7730,11 +7951,11 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -7749,7 +7970,7 @@
         <v>0</v>
       </c>
       <c r="R91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S91" s="3">
         <v>-100</v>
@@ -7761,13 +7982,13 @@
         <v>-100</v>
       </c>
       <c r="V91" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="W91" s="3">
         <v>-300</v>
       </c>
       <c r="X91" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="Y91" s="3">
         <v>-100</v>
@@ -7776,13 +7997,13 @@
         <v>-100</v>
       </c>
       <c r="AA91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
+      <c r="AC91" s="3">
+        <v>0</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
@@ -7796,8 +8017,11 @@
       <c r="AG91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7891,8 +8115,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7986,44 +8213,47 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-400</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>1200</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>4200</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
@@ -8034,7 +8264,7 @@
         <v>0</v>
       </c>
       <c r="R94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S94" s="3">
         <v>-100</v>
@@ -8046,28 +8276,28 @@
         <v>-100</v>
       </c>
       <c r="V94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W94" s="3">
         <v>-300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-13100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>1000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-900</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
+      <c r="AC94" s="3">
+        <v>0</v>
       </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
@@ -8081,8 +8311,11 @@
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8116,8 +8349,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8160,8 +8394,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -8211,8 +8445,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8306,8 +8543,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8401,8 +8641,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8496,88 +8739,91 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
-        <v>1800</v>
-      </c>
       <c r="H100" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>900</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-100</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-200</v>
       </c>
       <c r="N100" s="3">
         <v>-200</v>
       </c>
       <c r="O100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P100" s="3">
         <v>-500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>10700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1100</v>
-      </c>
-      <c r="T100" s="3">
-        <v>100</v>
       </c>
       <c r="U100" s="3">
         <v>100</v>
       </c>
       <c r="V100" s="3">
+        <v>100</v>
+      </c>
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-4100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>53600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2000</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
+      <c r="AC100" s="3">
+        <v>0</v>
       </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
@@ -8591,13 +8837,16 @@
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
@@ -8615,10 +8864,10 @@
         <v>0</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>600</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-200</v>
       </c>
       <c r="L101" s="3">
         <v>-200</v>
@@ -8627,55 +8876,55 @@
         <v>-200</v>
       </c>
       <c r="N101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O101" s="3">
         <v>900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-100</v>
       </c>
       <c r="V101" s="3">
         <v>-100</v>
       </c>
       <c r="W101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>0</v>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE101" s="3">
         <v>0</v>
@@ -8686,89 +8935,92 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>900</v>
+        <v>-1900</v>
       </c>
       <c r="E102" s="3">
         <v>900</v>
       </c>
       <c r="F102" s="3">
+        <v>900</v>
+      </c>
+      <c r="G102" s="3">
         <v>1800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-5500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-21500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>45800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>500</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8779,6 +9031,9 @@
         <v>3</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
